--- a/config/equips.xlsx
+++ b/config/equips.xlsx
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>翡翠の御守</t>
+          <t>翡翠御守</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>翡翠の御守</t>
+          <t>翡翠御守</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>翡翠の御守</t>
+          <t>翡翠御守</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>翡翠の御守</t>
+          <t>翡翠御守</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>翡翠の御守</t>
+          <t>翡翠御守</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>翡翠の御守</t>
+          <t>翡翠御守</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>翡翠の御守</t>
+          <t>翡翠御守</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>翡翠の御守</t>
+          <t>翡翠御守</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>翠星の御守</t>
+          <t>翠星御守</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>翠星の御守</t>
+          <t>翠星御守</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>翠星の御守</t>
+          <t>翠星御守</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>翠星の御守</t>
+          <t>翠星御守</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>翠星の御守</t>
+          <t>翠星御守</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>翠星の御守</t>
+          <t>翠星御守</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>翠星の御守</t>
+          <t>翠星御守</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>翠星の御守</t>
+          <t>翠星御守</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の御守</t>
+          <t>琉璃御守</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の御守</t>
+          <t>琉璃御守</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の御守</t>
+          <t>琉璃御守</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の御守</t>
+          <t>琉璃御守</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の御守</t>
+          <t>琉璃御守</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の御守</t>
+          <t>琉璃御守</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の御守</t>
+          <t>琉璃御守</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の御守</t>
+          <t>琉璃御守</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>翠玉の御守</t>
+          <t>翠玉御守</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>翠玉の御守</t>
+          <t>翠玉御守</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>翠玉の御守</t>
+          <t>翠玉御守</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>翠玉の御守</t>
+          <t>翠玉御守</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>翠玉の御守</t>
+          <t>翠玉御守</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>翠玉の御守</t>
+          <t>翠玉御守</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>翠玉の御守</t>
+          <t>翠玉御守</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>翠玉の御守</t>
+          <t>翠玉御守</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>彗星の御守</t>
+          <t>彗星的守护者</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>彗星の御守</t>
+          <t>彗星的守护者</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>彗星の御守</t>
+          <t>彗星的守护者</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>彗星の御守</t>
+          <t>彗星的守护者</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>彗星の御守</t>
+          <t>彗星的守护者</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>彗星の御守</t>
+          <t>彗星的守护者</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>彗星の御守</t>
+          <t>彗星的守护者</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>彗星の御守</t>
+          <t>彗星的守护者</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>精霊の御守</t>
+          <t>精灵的御守</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>精霊の御守</t>
+          <t>精灵的御守</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>精霊の御守</t>
+          <t>精灵的御守</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>精霊の御守</t>
+          <t>精灵的御守</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>精霊の御守</t>
+          <t>精灵的御守</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>精霊の御守</t>
+          <t>精灵的御守</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>精霊の御守</t>
+          <t>精灵的御守</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>精霊の御守</t>
+          <t>精灵的御守</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>翡翠の耳飾り</t>
+          <t>翡翠耳环</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>翡翠の耳飾り</t>
+          <t>翡翠耳环</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>翡翠の耳飾り</t>
+          <t>翡翠耳环</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>翡翠の耳飾り</t>
+          <t>翡翠耳环</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>翡翠の耳飾り</t>
+          <t>翡翠耳环</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>翡翠の耳飾り</t>
+          <t>翡翠耳环</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>翡翠の耳飾り</t>
+          <t>翡翠耳环</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>翡翠の耳飾り</t>
+          <t>翡翠耳环</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>翠星の耳飾り</t>
+          <t>翠星的耳环</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>翠星の耳飾り</t>
+          <t>翠星的耳环</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>翠星の耳飾り</t>
+          <t>翠星的耳环</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>翠星の耳飾り</t>
+          <t>翠星的耳环</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>翠星の耳飾り</t>
+          <t>翠星的耳环</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>翠星の耳飾り</t>
+          <t>翠星的耳环</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>翠星の耳飾り</t>
+          <t>翠星的耳环</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>翠星の耳飾り</t>
+          <t>翠星的耳环</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の耳飾り</t>
+          <t>琉璃耳环</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の耳飾り</t>
+          <t>琉璃耳环</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の耳飾り</t>
+          <t>琉璃耳环</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の耳飾り</t>
+          <t>琉璃耳环</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の耳飾り</t>
+          <t>琉璃耳环</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の耳飾り</t>
+          <t>琉璃耳环</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の耳飾り</t>
+          <t>琉璃耳环</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の耳飾り</t>
+          <t>琉璃耳环</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>翠玉の耳飾り</t>
+          <t>翠玉耳环</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>翠玉の耳飾り</t>
+          <t>翠玉耳环</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>翠玉の耳飾り</t>
+          <t>翠玉耳环</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>翠玉の耳飾り</t>
+          <t>翠玉耳环</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>翠玉の耳飾り</t>
+          <t>翠玉耳环</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>翠玉の耳飾り</t>
+          <t>翠玉耳环</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>翠玉の耳飾り</t>
+          <t>翠玉耳环</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>翠玉の耳飾り</t>
+          <t>翠玉耳环</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>彗星の耳飾り</t>
+          <t>彗星耳环</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>彗星の耳飾り</t>
+          <t>彗星耳环</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>彗星の耳飾り</t>
+          <t>彗星耳环</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>彗星の耳飾り</t>
+          <t>彗星耳环</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>彗星の耳飾り</t>
+          <t>彗星耳环</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>彗星の耳飾り</t>
+          <t>彗星耳环</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>彗星の耳飾り</t>
+          <t>彗星耳环</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>彗星の耳飾り</t>
+          <t>彗星耳环</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>精霊の耳飾り</t>
+          <t>精灵的耳环</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>精霊の耳飾り</t>
+          <t>精灵的耳环</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>精霊の耳飾り</t>
+          <t>精灵的耳环</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>精霊の耳飾り</t>
+          <t>精灵的耳环</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>精霊の耳飾り</t>
+          <t>精灵的耳环</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>精霊の耳飾り</t>
+          <t>精灵的耳环</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>精霊の耳飾り</t>
+          <t>精灵的耳环</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>精霊の耳飾り</t>
+          <t>精灵的耳环</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>翡翠の髪飾り</t>
+          <t>翡翠发饰</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>翡翠の髪飾り</t>
+          <t>翡翠发饰</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>翡翠の髪飾り</t>
+          <t>翡翠发饰</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>翡翠の髪飾り</t>
+          <t>翡翠发饰</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>翡翠の髪飾り</t>
+          <t>翡翠发饰</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>翡翠の髪飾り</t>
+          <t>翡翠发饰</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>翡翠の髪飾り</t>
+          <t>翡翠发饰</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>翡翠の髪飾り</t>
+          <t>翡翠发饰</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>翠星の髪飾り</t>
+          <t>翠星发饰</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>翠星の髪飾り</t>
+          <t>翠星发饰</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>翠星の髪飾り</t>
+          <t>翠星发饰</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>翠星の髪飾り</t>
+          <t>翠星发饰</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>翠星の髪飾り</t>
+          <t>翠星发饰</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>翠星の髪飾り</t>
+          <t>翠星发饰</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>翠星の髪飾り</t>
+          <t>翠星发饰</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>翠星の髪飾り</t>
+          <t>翠星发饰</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の髪飾り</t>
+          <t>琉璃发饰</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>瑠璃の髪飾り</t>
+          <t>琉璃发饰</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の髪飾り</t>
+          <t>琉璃发饰</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>瑠璃の髪飾り</t>
+          <t>琉璃发饰</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の髪飾り</t>
+          <t>琉璃发饰</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>瑠璃の髪飾り</t>
+          <t>琉璃发饰</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -17536,7 +17536,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の髪飾り</t>
+          <t>琉璃发饰</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>瑠璃の髪飾り</t>
+          <t>琉璃发饰</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -17803,7 +17803,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>翠玉の髪飾り</t>
+          <t>翠玉发饰</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>翠玉の髪飾り</t>
+          <t>翠玉发饰</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>翠玉の髪飾り</t>
+          <t>翠玉发饰</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18090,7 +18090,7 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>翠玉の髪飾り</t>
+          <t>翠玉发饰</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -18337,7 +18337,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>翠玉の髪飾り</t>
+          <t>翠玉发饰</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>翠玉の髪飾り</t>
+          <t>翠玉发饰</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -18604,7 +18604,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>翠玉の髪飾り</t>
+          <t>翠玉发饰</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>翠玉の髪飾り</t>
+          <t>翠玉发饰</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>彗星の髪飾り</t>
+          <t>彗星发饰</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>彗星の髪飾り</t>
+          <t>彗星发饰</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>彗星の髪飾り</t>
+          <t>彗星发饰</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>彗星の髪飾り</t>
+          <t>彗星发饰</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>彗星の髪飾り</t>
+          <t>彗星发饰</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>彗星の髪飾り</t>
+          <t>彗星发饰</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -19672,7 +19672,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>彗星の髪飾り</t>
+          <t>彗星发饰</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>彗星の髪飾り</t>
+          <t>彗星发饰</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>精霊の髪飾り</t>
+          <t>精灵发饰</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>精霊の髪飾り</t>
+          <t>精灵发饰</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20206,7 +20206,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>精霊の髪飾り</t>
+          <t>精灵发饰</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>精霊の髪飾り</t>
+          <t>精灵发饰</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>精霊の髪飾り</t>
+          <t>精灵发饰</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -20493,7 +20493,7 @@
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>精霊の髪飾り</t>
+          <t>精灵发饰</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>精霊の髪飾り</t>
+          <t>精灵发饰</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>精霊の髪飾り</t>
+          <t>精灵发饰</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -21007,7 +21007,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>翡翠の首飾り</t>
+          <t>翡翠项链</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>翡翠の首飾り</t>
+          <t>翡翠项链</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>翡翠の首飾り</t>
+          <t>翡翠项链</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>翡翠の首飾り</t>
+          <t>翡翠项链</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>翡翠の首飾り</t>
+          <t>翡翠项链</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>翡翠の首飾り</t>
+          <t>翡翠项链</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>翡翠の首飾り</t>
+          <t>翡翠项链</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>翡翠の首飾り</t>
+          <t>翡翠项链</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>翠星の首飾り</t>
+          <t>翠星项链</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -22095,7 +22095,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>翠星の首飾り</t>
+          <t>翠星项链</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>翠星の首飾り</t>
+          <t>翠星项链</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>翠星の首飾り</t>
+          <t>翠星项链</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>翠星の首飾り</t>
+          <t>翠星项链</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>翠星の首飾り</t>
+          <t>翠星项链</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>翠星の首飾り</t>
+          <t>翠星项链</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -22896,7 +22896,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>翠星の首飾り</t>
+          <t>翠星项链</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -23143,7 +23143,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の首飾り</t>
+          <t>琉璃项链</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の首飾り</t>
+          <t>琉璃项链</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の首飾り</t>
+          <t>琉璃项链</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の首飾り</t>
+          <t>琉璃项链</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の首飾り</t>
+          <t>琉璃项链</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -23697,7 +23697,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の首飾り</t>
+          <t>琉璃项链</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の首飾り</t>
+          <t>琉璃项链</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -23964,7 +23964,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>瑠璃の首飾り</t>
+          <t>琉璃项链</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>翠玉の首飾り</t>
+          <t>翠玉项链</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>翠玉の首飾り</t>
+          <t>翠玉项链</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -24478,7 +24478,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>翠玉の首飾り</t>
+          <t>翠玉项链</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>翠玉の首飾り</t>
+          <t>翠玉项链</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>翠玉の首飾り</t>
+          <t>翠玉项链</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>翠玉の首飾り</t>
+          <t>翠玉项链</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>翠玉の首飾り</t>
+          <t>翠玉项链</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -25032,7 +25032,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>翠玉の首飾り</t>
+          <t>翠玉项链</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>彗星の首飾り</t>
+          <t>彗星项链</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -25299,7 +25299,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>彗星の首飾り</t>
+          <t>彗星项链</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -25546,7 +25546,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>彗星の首飾り</t>
+          <t>彗星项链</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -25566,7 +25566,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>彗星の首飾り</t>
+          <t>彗星项链</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -25813,7 +25813,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>彗星の首飾り</t>
+          <t>彗星项链</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -25833,7 +25833,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>彗星の首飾り</t>
+          <t>彗星项链</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -26080,7 +26080,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>彗星の首飾り</t>
+          <t>彗星项链</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -26100,7 +26100,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>彗星の首飾り</t>
+          <t>彗星项链</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>精霊の首飾り</t>
+          <t>精灵项链</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -26367,7 +26367,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>精霊の首飾り</t>
+          <t>精灵项链</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>精霊の首飾り</t>
+          <t>精灵项链</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -26634,7 +26634,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>精霊の首飾り</t>
+          <t>精灵项链</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -26881,7 +26881,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>精霊の首飾り</t>
+          <t>精灵项链</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>精霊の首飾り</t>
+          <t>精灵项链</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>精霊の首飾り</t>
+          <t>精灵项链</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>精霊の首飾り</t>
+          <t>精灵项链</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
